--- a/ontology/contingency-data/京东三期/项目管理/问题/输出结果/问题信息.xlsx
+++ b/ontology/contingency-data/京东三期/项目管理/问题/输出结果/问题信息.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>2026-06-13 18:01:58</t>
+          <t>2026-06-13 18:18:23</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>2026-06-13 18:01:58</t>
+          <t>2026-06-13 18:18:23</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
